--- a/output/2026-09-05_17_Italia_Sicilia_Metalworking_Lavorazioni_Metalliche.xlsx
+++ b/output/2026-09-05_17_Italia_Sicilia_Metalworking_Lavorazioni_Metalliche.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Impianti di aspirazione industriale, depurazione aria, ventilazione, verniciatura. Fetch diretto del sito non riuscito (proxy egress bloccato); dati basati sulla fonte di raccolta iniziale, coerenti con indirizzo/contatti forniti.</t>
+          <t>Impianti di aspirazione industriale, depurazione aria, ventilazione, verniciatura. Fetch diretto del sito non riuscito (proxy egress bloccato); dati basati sulla fonte di raccolta iniziale, coerenti con indirizzo/contatti forniti. [DUPLICATO — vedi anche: 2026-09-05_12_Italia_Sicilia_Depolverazione_Trattamento_aria.xlsx]</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -533,7 +533,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Nonostante il nome contenga 'Officina', la categoria prodotto dichiarata è impianti di aspirazione/depurazione aria, canalizzazioni, cappe, filtri (profilo da installatore/rivenditore, non officina meccanica conto terzi). Verificare con contatto diretto per escludere che sia in realtà un'officina cliente finale.</t>
+          <t>Nonostante il nome contenga 'Officina', la categoria prodotto dichiarata è impianti di aspirazione/depurazione aria, canalizzazioni, cappe, filtri (profilo da installatore/rivenditore, non officina meccanica conto terzi). Verificare con contatto diretto per escludere che sia in realtà un'officina cliente finale. [DUPLICATO — vedi anche: 2026-09-05_12_Italia_Sicilia_Depolverazione_Trattamento_aria.xlsx]</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -652,10 +652,9 @@
           <t>091 7835507 / 393 8881787</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Cappe in acciaio inox, aspiratori industriali, condizionamento, riscaldamento. Sito non raggiungibile (DNS non risolto) con gli strumenti disponibili in questo ambiente.</t>
+          <t>Cappe in acciaio inox, aspiratori industriali, condizionamento, riscaldamento. Sito non raggiungibile (DNS non risolto) con gli strumenti disponibili in questo ambiente. [DUPLICATO — vedi anche: 2026-09-05_13_Italia_Sicilia_Impiantistica_aspirazione_industriale.xlsx]</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -739,7 +738,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Macchine per pulizia industriale, aspiratori industriali, aspiraliquidi, motoscope.</t>
+          <t>Macchine per pulizia industriale, aspiratori industriali, aspiraliquidi, motoscope. [DUPLICATO — vedi anche: 2026-09-05_11_Italia_Sicilia_Cleaning.xlsx]</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -811,11 +810,9 @@
           <t>Metalworking / Lavorazioni Metalliche</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr"/>
-      <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Vendita e noleggio macchine per pulizia industriale (lavasciuga, aspiratori, idropulitrici). Nessun contatto telefonico/email né indirizzo specifico disponibile nella fonte raccolta; verificare esistenza e recapiti diretti prima del contatto commerciale.</t>
+          <t>Vendita e noleggio macchine per pulizia industriale (lavasciuga, aspiratori, idropulitrici). Nessun contatto telefonico/email né indirizzo specifico disponibile nella fonte raccolta; verificare esistenza e recapiti diretti prima del contatto commerciale. [DUPLICATO — vedi anche: 2026-09-05_11_Italia_Sicilia_Cleaning.xlsx]</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -887,11 +884,9 @@
           <t>Metalworking / Lavorazioni Metalliche</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr"/>
-      <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Ingrosso macchine per pulizia industriale, incluso aspiratori industriali (rete PerPulire). Nessun telefono/email disponibile nella fonte raccolta.</t>
+          <t>Ingrosso macchine per pulizia industriale, incluso aspiratori industriali (rete PerPulire). Nessun telefono/email disponibile nella fonte raccolta. [DUPLICATO — vedi anche: 2026-09-05_11_Italia_Sicilia_Cleaning.xlsx]</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -921,11 +916,9 @@
           <t>Metalworking / Lavorazioni Metalliche</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr"/>
-      <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Commercio all'ingrosso di detergenti e prodotti per la pulizia, aspiratori industriali, lavapavimenti, antinfortunistica (Piraino, ME). Presenza solo su Facebook, nessun sito web proprio né contatti diretti nella fonte raccolta.</t>
+          <t>Commercio all'ingrosso di detergenti e prodotti per la pulizia, aspiratori industriali, lavapavimenti, antinfortunistica (Piraino, ME). Presenza solo su Facebook, nessun sito web proprio né contatti diretti nella fonte raccolta. [DUPLICATO — vedi anche: 2026-09-02_21_Italia_Molise_Metalworking_Lavorazioni_Metalliche.xlsx]</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -940,7 +933,6 @@
           <t>Cleaning's Systems S.n.c. dei F.lli Di Falco</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr"/>
       <c r="C14" t="inlineStr">
         <is>
           <t>Siracusa</t>
@@ -956,7 +948,6 @@
           <t>0931 759311</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr">
         <is>
           <t>Concessionaria Taski - aspiratori/macchine di pulizia industriale.</t>
@@ -974,7 +965,6 @@
           <t>Elettromeccanica S.r.l.</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr"/>
       <c r="C15" t="inlineStr">
         <is>
           <t>Siracusa</t>
@@ -990,7 +980,6 @@
           <t>0931 21650</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr"/>
       <c r="G15" t="inlineStr">
         <is>
           <t>Impianti ed attrezzature aria compressa.</t>
@@ -1008,7 +997,6 @@
           <t>Arca di Arfo' Salvatore e Capozio Pierpaolo S.n.c.</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr"/>
       <c r="C16" t="inlineStr">
         <is>
           <t>Siracusa</t>
@@ -1024,7 +1012,6 @@
           <t>0931 468002</t>
         </is>
       </c>
-      <c r="F16" t="inlineStr"/>
       <c r="G16" t="inlineStr">
         <is>
           <t>Impianti ed attrezzature aria compressa. Nessun sito web disponibile.</t>
@@ -1062,7 +1049,6 @@
           <t>0932 666481 / 333 9265602</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr"/>
       <c r="G17" t="inlineStr">
         <is>
           <t>Vendita/noleggio/manutenzione attrezzature per pulizia industriale, movimentazione e cantiere.</t>
@@ -1100,10 +1086,9 @@
           <t>0932 622978</t>
         </is>
       </c>
-      <c r="F18" t="inlineStr"/>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Utensileria, ferramenta, compressori, aspiratori (rivenditore multimarca).</t>
+          <t>Utensileria, ferramenta, compressori, aspiratori (rivenditore multimarca). [DUPLICATO — vedi anche: 2026-09-05_16_Italia_Sicilia_Utensilerie_e_Macchine_Utensili.xlsx]</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1145,7 +1130,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Vendita attrezzature, utensili, macchine e materiali per edilizia, industria e settore meccanico, inclusi compressori, aria compressa, DPI.</t>
+          <t>Vendita attrezzature, utensili, macchine e materiali per edilizia, industria e settore meccanico, inclusi compressori, aria compressa, DPI. [DUPLICATO — vedi anche: 2026-09-05_16_Italia_Sicilia_Utensilerie_e_Macchine_Utensili.xlsx]</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">

--- a/output/2026-09-05_17_Italia_Sicilia_Metalworking_Lavorazioni_Metalliche.xlsx
+++ b/output/2026-09-05_17_Italia_Sicilia_Metalworking_Lavorazioni_Metalliche.xlsx
@@ -580,7 +580,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (07/09/2026)</t>
         </is>
       </c>
     </row>
@@ -622,7 +622,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (07/09/2026)</t>
         </is>
       </c>
     </row>
@@ -701,7 +701,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (07/09/2026)</t>
         </is>
       </c>
     </row>
@@ -785,7 +785,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (07/09/2026)</t>
         </is>
       </c>
     </row>
@@ -859,7 +859,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (07/09/2026)</t>
         </is>
       </c>
     </row>
@@ -1019,7 +1019,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (07/09/2026)</t>
         </is>
       </c>
     </row>
@@ -1056,7 +1056,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (07/09/2026)</t>
         </is>
       </c>
     </row>
